--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260812.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260812.xlsx
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>13,510,000</t>
+          <t>34,120,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>34,120,000</t>
+          <t>13,510,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>台指期</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>台指期</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>41,370,000</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>41,370,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
